--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1630,6 +1630,835 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129593957</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>458914</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6987454</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129593956</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>458952</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6987377</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129593952</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>459451</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6987552</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129593959</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>459239</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6987594</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129593962</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57831</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>459440</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6987567</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129593963</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91549</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>458910</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6987395</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129593958</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>458958</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6987524</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129593960</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>459243</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6987586</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -2051,57 +2051,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129593962</v>
+        <v>129593963</v>
       </c>
       <c r="B15" t="n">
-        <v>57831</v>
+        <v>91549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459440</v>
+        <v>458910</v>
       </c>
       <c r="R15" t="n">
-        <v>6987567</v>
+        <v>6987395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,45 +2148,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129593963</v>
+        <v>129593962</v>
       </c>
       <c r="B16" t="n">
-        <v>91549</v>
+        <v>57831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458910</v>
+        <v>459440</v>
       </c>
       <c r="R16" t="n">
-        <v>6987395</v>
+        <v>6987567</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -1635,7 +1635,7 @@
         <v>129593957</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>129593956</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129593952</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>129593959</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129593963</v>
       </c>
       <c r="B15" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129593962</v>
       </c>
       <c r="B16" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>129593958</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129593960</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -1635,7 +1635,7 @@
         <v>129593957</v>
       </c>
       <c r="B11" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>129593956</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129593952</v>
       </c>
       <c r="B13" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>129593959</v>
       </c>
       <c r="B14" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129593963</v>
       </c>
       <c r="B15" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129593962</v>
       </c>
       <c r="B16" t="n">
-        <v>57834</v>
+        <v>57839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>129593958</v>
       </c>
       <c r="B17" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129593960</v>
       </c>
       <c r="B18" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -1635,7 +1635,7 @@
         <v>129593957</v>
       </c>
       <c r="B11" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>129593956</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129593952</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>129593959</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,45 +2051,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129593963</v>
+        <v>129593962</v>
       </c>
       <c r="B15" t="n">
-        <v>91583</v>
+        <v>57840</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458910</v>
+        <v>459440</v>
       </c>
       <c r="R15" t="n">
-        <v>6987395</v>
+        <v>6987567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,57 +2160,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129593962</v>
+        <v>129593963</v>
       </c>
       <c r="B16" t="n">
-        <v>57839</v>
+        <v>91584</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459440</v>
+        <v>458910</v>
       </c>
       <c r="R16" t="n">
-        <v>6987567</v>
+        <v>6987395</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
         <v>129593958</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129593960</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -2051,57 +2051,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129593962</v>
+        <v>129593963</v>
       </c>
       <c r="B15" t="n">
-        <v>57840</v>
+        <v>91589</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459440</v>
+        <v>458910</v>
       </c>
       <c r="R15" t="n">
-        <v>6987567</v>
+        <v>6987395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,45 +2148,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129593963</v>
+        <v>129593962</v>
       </c>
       <c r="B16" t="n">
-        <v>91584</v>
+        <v>57840</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458910</v>
+        <v>459440</v>
       </c>
       <c r="R16" t="n">
-        <v>6987395</v>
+        <v>6987567</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -2051,45 +2051,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129593963</v>
+        <v>129593962</v>
       </c>
       <c r="B15" t="n">
-        <v>91589</v>
+        <v>57840</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458910</v>
+        <v>459440</v>
       </c>
       <c r="R15" t="n">
-        <v>6987395</v>
+        <v>6987567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,57 +2160,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129593962</v>
+        <v>129593963</v>
       </c>
       <c r="B16" t="n">
-        <v>57840</v>
+        <v>91589</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459440</v>
+        <v>458910</v>
       </c>
       <c r="R16" t="n">
-        <v>6987567</v>
+        <v>6987395</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -2051,57 +2051,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129593962</v>
+        <v>129593963</v>
       </c>
       <c r="B15" t="n">
-        <v>57840</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459440</v>
+        <v>458910</v>
       </c>
       <c r="R15" t="n">
-        <v>6987567</v>
+        <v>6987395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,45 +2148,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129593963</v>
+        <v>129593962</v>
       </c>
       <c r="B16" t="n">
-        <v>91589</v>
+        <v>57840</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458910</v>
+        <v>459440</v>
       </c>
       <c r="R16" t="n">
-        <v>6987395</v>
+        <v>6987567</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -2054,7 +2054,7 @@
         <v>129593963</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -1635,7 +1635,7 @@
         <v>129593957</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>129593956</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129593952</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>129593959</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>129593963</v>
       </c>
       <c r="B15" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>129593962</v>
       </c>
       <c r="B16" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>129593958</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129593960</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -1635,7 +1635,7 @@
         <v>129593957</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>129593956</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>129593952</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>129593959</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2051,45 +2051,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129593963</v>
+        <v>129593962</v>
       </c>
       <c r="B15" t="n">
-        <v>91598</v>
+        <v>57844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>458910</v>
+        <v>459440</v>
       </c>
       <c r="R15" t="n">
-        <v>6987395</v>
+        <v>6987567</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,57 +2160,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129593962</v>
+        <v>129593963</v>
       </c>
       <c r="B16" t="n">
-        <v>57841</v>
+        <v>91601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>459440</v>
+        <v>458910</v>
       </c>
       <c r="R16" t="n">
-        <v>6987567</v>
+        <v>6987395</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,7 +2260,7 @@
         <v>129593958</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>129593960</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121128967</v>
+        <v>129593963</v>
       </c>
       <c r="B2" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459193</v>
+        <v>458910</v>
       </c>
       <c r="R2" t="n">
-        <v>6987308</v>
+        <v>6987395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121129187</v>
+        <v>121128992</v>
       </c>
       <c r="B3" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +807,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459243</v>
+        <v>459186</v>
       </c>
       <c r="R3" t="n">
-        <v>6987320</v>
+        <v>6987297</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,50 +879,49 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121128992</v>
+        <v>121210323</v>
       </c>
       <c r="B4" t="n">
-        <v>90713</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459186</v>
+        <v>459198</v>
       </c>
       <c r="R4" t="n">
-        <v>6987297</v>
+        <v>6987270</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -969,22 +948,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack efter hästmyror, något äldre hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +973,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jenny Persson</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121210323</v>
+        <v>129593956</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,16 +996,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1044,24 +1013,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459198</v>
+        <v>458952</v>
       </c>
       <c r="R5" t="n">
-        <v>6987270</v>
+        <v>6987377</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,17 +1066,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Hack efter hästmyror, något äldre hack</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,65 +1086,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121210333</v>
+        <v>129593957</v>
       </c>
       <c r="B6" t="n">
-        <v>74706</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>492</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459276</v>
+        <v>458914</v>
       </c>
       <c r="R6" t="n">
-        <v>6987463</v>
+        <v>6987454</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1192,12 +1163,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,27 +1188,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121210345</v>
+        <v>129593958</v>
       </c>
       <c r="B7" t="n">
-        <v>74707</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,37 +1211,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>459225</v>
+        <v>458958</v>
       </c>
       <c r="R7" t="n">
-        <v>6987464</v>
+        <v>6987524</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,12 +1265,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,27 +1290,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121210346</v>
+        <v>121210345</v>
       </c>
       <c r="B8" t="n">
-        <v>74707</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1366,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>459235</v>
+        <v>459225</v>
       </c>
       <c r="R8" t="n">
-        <v>6987465</v>
+        <v>6987464</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1428,15 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121210329</v>
+        <v>121210346</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1468,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>459208</v>
+        <v>459235</v>
       </c>
       <c r="R9" t="n">
-        <v>6987442</v>
+        <v>6987465</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1533,12 +1499,7 @@
         <v>121210347</v>
       </c>
       <c r="B10" t="n">
-        <v>74707</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,48 +1593,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129593957</v>
+        <v>121210333</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>83298</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>492</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Strömborgen, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>458914</v>
+        <v>459276</v>
       </c>
       <c r="R11" t="n">
-        <v>6987454</v>
+        <v>6987463</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1697,17 +1658,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1722,76 +1678,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129593956</v>
+        <v>121210324</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>92605</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Strömborgen, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>458952</v>
+        <v>459250</v>
       </c>
       <c r="R12" t="n">
-        <v>6987377</v>
+        <v>6987362</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1815,12 +1755,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,22 +1775,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129593952</v>
+        <v>121210352</v>
       </c>
       <c r="B13" t="n">
-        <v>57740</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,37 +1798,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Strömborgen, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>459451</v>
+        <v>459272</v>
       </c>
       <c r="R13" t="n">
-        <v>6987552</v>
+        <v>6987314</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1912,17 +1852,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1937,22 +1872,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129593959</v>
+        <v>121210336</v>
       </c>
       <c r="B14" t="n">
-        <v>57740</v>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1960,37 +1895,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Strömborgen, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>459239</v>
+        <v>459289</v>
       </c>
       <c r="R14" t="n">
-        <v>6987594</v>
+        <v>6987454</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2014,17 +1949,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2039,69 +1969,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Klas Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129593962</v>
+        <v>129593961</v>
       </c>
       <c r="B15" t="n">
-        <v>57844</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Strömborgen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459440</v>
+        <v>459426</v>
       </c>
       <c r="R15" t="n">
-        <v>6987567</v>
+        <v>6987645</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2160,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129593963</v>
+        <v>129593952</v>
       </c>
       <c r="B16" t="n">
-        <v>91601</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2171,21 +2089,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2195,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>458910</v>
+        <v>459451</v>
       </c>
       <c r="R16" t="n">
-        <v>6987395</v>
+        <v>6987552</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,6 +2149,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2257,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129593958</v>
+        <v>129593959</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2292,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>458958</v>
+        <v>459239</v>
       </c>
       <c r="R17" t="n">
-        <v>6987524</v>
+        <v>6987594</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,7 +2255,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,7 +2285,7 @@
         <v>129593960</v>
       </c>
       <c r="B18" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,6 +2381,212 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129593962</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Strömborgen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>459440</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6987567</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121210326</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Strömborgsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>459248</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6987371</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-11-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39288-2025 artfynd.xlsx
+++ b/artfynd/A 39288-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210345</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210346</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210347</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210333</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210324</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129593963</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,6 +1396,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121128992</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1458,6 +1498,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210352</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210336</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1652,6 +1702,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129593961</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1758,6 +1813,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210323</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1860,6 +1920,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129593952</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1973,6 +2038,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129593956</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,6 +2145,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129593957</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2177,6 +2252,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129593958</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2279,6 +2359,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129593959</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2381,6 +2466,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129593960</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2490,6 +2580,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129593962</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2587,8 +2682,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121210326</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>